--- a/data/availability/projects/dorra/the-address-east.xlsx
+++ b/data/availability/projects/dorra/the-address-east.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>On Hold / Sold Out</t>
+          <t>Fact sheet inventory for the-address-east</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,6 +543,56 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>payment_plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>the-address-east</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>160</v>
+      </c>
+      <c r="F2" t="n">
+        <v>160</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Full finishing</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>6 months</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>15% / 5 yrs</t>
         </is>
       </c>
     </row>
@@ -557,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,6 +674,63 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>the-address-east</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Apartment</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ADE-3BR</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Full finishing</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>160</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>9500000</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>6 months</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>15% / 5 yrs</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Available</t>
         </is>
       </c>
     </row>
